--- a/esempi/esempio_turno_chiuso.xlsx
+++ b/esempi/esempio_turno_chiuso.xlsx
@@ -1958,7 +1958,7 @@
       <c r="G20" s="88" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="84" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="J20" s="87" t="n"/>
       <c r="K20" s="88" t="n"/>
@@ -2098,9 +2098,7 @@
       <c r="F24" s="87" t="n"/>
       <c r="G24" s="88" t="n"/>
       <c r="H24" s="6" t="n"/>
-      <c r="I24" s="74" t="n">
-        <v>0.5871759259259259</v>
-      </c>
+      <c r="I24" s="74" t="n"/>
       <c r="J24" s="87" t="n"/>
       <c r="K24" s="88" t="n"/>
       <c r="L24" s="1" t="inlineStr">
@@ -2238,7 +2236,9 @@
       <c r="F28" s="87" t="n"/>
       <c r="G28" s="88" t="n"/>
       <c r="H28" s="6" t="n"/>
-      <c r="I28" s="45" t="n"/>
+      <c r="I28" s="45" t="n">
+        <v>20</v>
+      </c>
       <c r="J28" s="87" t="n"/>
       <c r="K28" s="88" t="n"/>
       <c r="L28" s="100" t="n"/>
@@ -2446,7 +2446,7 @@
       <c r="B34" s="87" t="n"/>
       <c r="C34" s="88" t="n"/>
       <c r="D34" s="6" t="n">
-        <v>150.5</v>
+        <v>130.5</v>
       </c>
       <c r="E34" s="55" t="inlineStr">
         <is>
